--- a/docs/review/packs/chapter-3.17.xlsx
+++ b/docs/review/packs/chapter-3.17.xlsx
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -4279,7 +4279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4372,7 +4372,102 @@
       </c>
       <c r="H2" s="7" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>3.17.2-F1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>3.17.2</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>thirty degrees</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>That dissociation is the mechanical basis of the dial test: rotation at thirty degrees and at ninety degrees separates an isolated posterolateral injury from a combined one.</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>3.17.2-F2</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>3.17.2</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ninety degrees</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>That dissociation is the mechanical basis of the dial test: rotation at thirty degrees and at ninety degrees separates an isolated posterolateral injury from a combined one.</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>3.17.5-F1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>3.17.5</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>frcs</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>thirty degrees</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Comparing thirty degrees with ninety separates an isolated corner injury from a combined one, and the test exists because the sectioning work showed the pattern.</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F3:F5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed decision" error="Use one of: VERIFIED, CORRECTED, REMOVED" type="list">
+      <formula1>"VERIFIED,CORRECTED,REMOVED"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4415,7 +4510,7 @@
         <v/>
       </c>
       <c r="C2" s="3">
-        <f>0</f>
+        <f>3</f>
         <v/>
       </c>
     </row>
@@ -4430,7 +4525,7 @@
         <v/>
       </c>
       <c r="C3" s="3">
-        <f>COUNTIF(Measurements!F3:F2,"&lt;&gt;")</f>
+        <f>COUNTIF(Measurements!F3:F5,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -4505,7 +4600,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr"/>
       <c r="C9" s="3">
-        <f>COUNTIF(Measurements!F3:F2,"VERIFIED")</f>
+        <f>COUNTIF(Measurements!F3:F5,"VERIFIED")</f>
         <v/>
       </c>
     </row>
@@ -4517,7 +4612,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr"/>
       <c r="C10" s="3">
-        <f>COUNTIF(Measurements!F3:F2,"CORRECTED")</f>
+        <f>COUNTIF(Measurements!F3:F5,"CORRECTED")</f>
         <v/>
       </c>
     </row>
@@ -4529,7 +4624,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr"/>
       <c r="C11" s="3">
-        <f>COUNTIF(Measurements!F3:F2,"REMOVED")</f>
+        <f>COUNTIF(Measurements!F3:F5,"REMOVED")</f>
         <v/>
       </c>
     </row>
